--- a/docs/قالب-وصف-وظيفي-مبيعات-الوقود.xlsx
+++ b/docs/قالب-وصف-وظيفي-مبيعات-الوقود.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="208">
   <si>
     <t xml:space="preserve">الوصف الوظيفي — أخصائي مبيعات الوقود</t>
   </si>
   <si>
-    <t xml:space="preserve">قالب عام قابل للتكييف على أي منطقة أو قناة — الخانات الصفراء تُعبَّأ</t>
+    <t xml:space="preserve">قالب عام قابل للتكييف على أي منطقة أو قناة — الخانات الملوّنة تُعبَّأ</t>
   </si>
   <si>
     <t xml:space="preserve">① بيانات الوظيفة</t>
@@ -75,7 +75,13 @@
     <t xml:space="preserve">② الغرض من الوظيفة</t>
   </si>
   <si>
-    <t xml:space="preserve">تنمية حجم مبيعات الوقود للعملاء من المنشآت وأصحاب الأساطيل داخل النطاق المحدد، عبر التعاقد المباشر وتثبيت الحجم القائم، بما يحقق نمواً صافياً في الهامش لا مجرد تحويل حجم قائم إلى عقود مخفَّضة.</t>
+    <t xml:space="preserve">تنمية حجم مبيعات الوقود للعملاء من المنشآت وأصحاب الأساطيل داخل النطاق المحدد،</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبر التعاقد المباشر وتثبيت الحجم القائم بشرط نمو موثّق فوق خط الأساس،</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بما يحقق نمواً صافياً في الهامش لا مجرد تحويل حجم قائم إلى عقود مخفَّضة.</t>
   </si>
   <si>
     <t xml:space="preserve">③ المسؤوليات الرئيسية</t>
@@ -651,7 +657,7 @@
     <numFmt numFmtId="165" formatCode="0%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,43 +683,45 @@
     <font>
       <b val="true"/>
       <sz val="16"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
+      <color rgb="FF55565A"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF44546A"/>
-      <name val="Arial"/>
+      <color rgb="FF6E6A64"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
+      <color rgb="FFF5831F"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <name val="Arial"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color rgb="FF3E6E8E"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -721,21 +729,28 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <color rgb="FF3D3D3D"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
+      <color rgb="FF55565A"/>
+      <name val="DIN Next Arabic"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -743,21 +758,21 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
-      <name val="Arial"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF44546A"/>
-      <name val="Arial"/>
+      <color rgb="FF9B968E"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
+      <color rgb="FF2E8B6F"/>
+      <name val="DIN Next Arabic"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -771,50 +786,50 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFD9E2F3"/>
+        <fgColor rgb="FFF5831F"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFBEEE0"/>
+        <bgColor rgb="FFF5F2ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333399"/>
+        <fgColor rgb="FFFCE7C8"/>
+        <bgColor rgb="FFFBEEE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FFFFE699"/>
+        <fgColor rgb="FF55565A"/>
+        <bgColor rgb="FF6E6A64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
-        <bgColor rgb="FFD9E2F3"/>
+        <fgColor rgb="FFF2DAD4"/>
+        <bgColor rgb="FFE3DCD1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFD6E9E1"/>
+        <bgColor rgb="FFEDE7DE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
-        <bgColor rgb="FFF8CBAD"/>
+        <fgColor rgb="FFEDE7DE"/>
+        <bgColor rgb="FFFBEEE0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFF5F2ED"/>
+        <bgColor rgb="FFFBEEE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -828,29 +843,29 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFE3DCD1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -880,7 +895,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -893,7 +908,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -901,15 +920,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -933,15 +952,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -949,83 +968,83 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="2"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1041,31 +1060,31 @@
   <dxfs count="2">
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="DIN Next Arabic"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF9A3E2C"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFF2DAD4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
+        <name val="DIN Next Arabic"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF375623"/>
+        <color rgb="FF1F5E4A"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFD6E9E1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1085,49 +1104,49 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF1F5E4A"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFDDEBF7"/>
+      <rgbColor rgb="FFFBEEE0"/>
+      <rgbColor rgb="FFF5F2ED"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E2F3"/>
+      <rgbColor rgb="FFE3DCD1"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF3E6E8E"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6E0B4"/>
-      <rgbColor rgb="FFFFE699"/>
+      <rgbColor rgb="FFEDE7DE"/>
+      <rgbColor rgb="FFD6E9E1"/>
+      <rgbColor rgb="FFFCE7C8"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF8CBAD"/>
+      <rgbColor rgb="FFF2DAD4"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFF5831F"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF44546A"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF6E6A64"/>
+      <rgbColor rgb="FF9B968E"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF2E8B6F"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF9A3E2C"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF375623"/>
+      <rgbColor rgb="FF55565A"/>
+      <rgbColor rgb="FF3D3D3D"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1311,9 +1330,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -1337,7 +1356,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1351,10 +1370,8 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
+    <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -1365,752 +1382,783 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="C12" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
+      <c r="D21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="B22" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="8" t="s">
+      <c r="C22" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
+      <c r="D22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B23" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+      <c r="B36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="B37" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+      <c r="B38" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+    </row>
+    <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
+    </row>
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-    </row>
-    <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-    </row>
-    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-    </row>
-    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44" s="10" t="s">
+      <c r="B47" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="16" t="s">
+      <c r="C47" s="11" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C47" s="17" t="s">
+      <c r="D47" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-    </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C48" s="17" t="s">
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-    </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C49" s="17" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C50" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-    </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C50" s="17" t="s">
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C51" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="18" t="s">
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C52" s="18" t="s">
         <v>99</v>
       </c>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-    </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C54" s="17" t="s">
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-    </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C55" s="17" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C56" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-    </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C56" s="17" t="s">
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C57" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+    </row>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C58" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C59" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="B14:J15"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="C47:J47"/>
-    <mergeCell ref="C48:J48"/>
-    <mergeCell ref="C49:J49"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A40:J40"/>
     <mergeCell ref="C50:J50"/>
+    <mergeCell ref="C51:J51"/>
+    <mergeCell ref="C52:J52"/>
     <mergeCell ref="C53:J53"/>
-    <mergeCell ref="C54:J54"/>
-    <mergeCell ref="C55:J55"/>
     <mergeCell ref="C56:J56"/>
+    <mergeCell ref="C57:J57"/>
+    <mergeCell ref="C58:J58"/>
+    <mergeCell ref="C59:J59"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2121,9 +2169,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2140,7 +2188,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2153,9 +2201,9 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2168,521 +2216,534 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
+      <c r="H4" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="B5" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="C5" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="D5" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="E5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="10" t="s">
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="F6" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="B7" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="C7" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="20" t="n">
+      <c r="D7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="21" t="n">
         <v>0.15</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="B8" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G7" s="20" t="n">
+      <c r="C8" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="B9" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="C9" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" s="20" t="n">
+      <c r="D9" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="B10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" s="20" t="n">
+      <c r="C10" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="B11" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="20" t="n">
+      <c r="C11" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="B12" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="C12" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="D12" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="21" t="n">
         <v>0.07</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B13" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G12" s="20" t="n">
+      <c r="G13" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="B14" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G13" s="20" t="n">
+      <c r="C14" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="B15" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14" s="20" t="n">
+      <c r="C15" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="21" t="n">
         <v>0.02</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <f aca="false">SUM(G4:G14)</f>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <f aca="false">SUM(G5:G15)</f>
         <v>1</v>
       </c>
-      <c r="H15" s="26" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C18" s="17" t="s">
+      <c r="H16" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="17" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
+      <c r="C19" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C20" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
+      <c r="C20" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C21" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="18" t="s">
+      <c r="C21" s="18" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C24" s="17" t="s">
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C22" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="19" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C25" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
+      <c r="C25" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C26" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
+      <c r="C26" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C27" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="C18:K18"/>
     <mergeCell ref="C19:K19"/>
     <mergeCell ref="C20:K20"/>
     <mergeCell ref="C21:K21"/>
-    <mergeCell ref="C24:K24"/>
+    <mergeCell ref="C22:K22"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C26:K26"/>
+    <mergeCell ref="C27:K27"/>
   </mergeCells>
-  <conditionalFormatting sqref="G15">
+  <conditionalFormatting sqref="G16">
     <cfRule type="cellIs" priority="2" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F4:F14" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F15" type="list">
       <formula1>"أعلى أفضل,أقل أفضل"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2693,9 +2754,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2708,7 +2769,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2719,9 +2780,9 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2732,10 +2793,8 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>176</v>
-      </c>
+    <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -2745,594 +2804,607 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="27" t="s">
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="27" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="C5" s="22"/>
+      <c r="D5" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="n">
+      <c r="H8" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="29" t="str">
-        <f aca="false">'مؤشرات الأداء'!B4</f>
+      <c r="B9" s="30" t="str">
+        <f aca="false">'مؤشرات الأداء'!B5</f>
         <v>الحجم المتعاقَد</v>
       </c>
-      <c r="C8" s="29" t="str">
-        <f aca="false">'مؤشرات الأداء'!F4</f>
-        <v>أعلى أفضل</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <f aca="false">'مؤشرات الأداء'!G4</f>
-        <v>0.15</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <f aca="false">'مؤشرات الأداء'!H4</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="31" t="str">
-        <f aca="false">IFERROR(IF(OR($F8="",$E8=""),"",IF($C8="أقل أفضل",$E8/$F8,$F8/$E8)),"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="32" t="str">
-        <f aca="false">IF($G8="","",MIN($G8,1.2)*$D8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="21"/>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="29" t="str">
-        <f aca="false">'مؤشرات الأداء'!B5</f>
-        <v>الحجم الصافي المضاف</v>
-      </c>
-      <c r="C9" s="29" t="str">
+      <c r="C9" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F5</f>
         <v>أعلى أفضل</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G5</f>
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H5</f>
         <v>0</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="31" t="str">
+      <c r="F9" s="22"/>
+      <c r="G9" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F9="",$E9=""),"",IF($C9="أقل أفضل",$E9/$F9,$F9/$E9)),"")</f>
         <v/>
       </c>
-      <c r="H9" s="32" t="str">
+      <c r="H9" s="33" t="str">
         <f aca="false">IF($G9="","",MIN($G9,1.2)*$D9)</f>
         <v/>
       </c>
-      <c r="I9" s="21"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="29" t="str">
+      <c r="A10" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B6</f>
-        <v>هامش المساهمة المتحقق</v>
-      </c>
-      <c r="C10" s="29" t="str">
+        <v>الحجم الصافي المضاف</v>
+      </c>
+      <c r="C10" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F6</f>
         <v>أعلى أفضل</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G6</f>
-        <v>0.15</v>
-      </c>
-      <c r="E10" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H6</f>
         <v>0</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="31" t="str">
+      <c r="F10" s="22"/>
+      <c r="G10" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F10="",$E10=""),"",IF($C10="أقل أفضل",$E10/$F10,$F10/$E10)),"")</f>
         <v/>
       </c>
-      <c r="H10" s="32" t="str">
+      <c r="H10" s="33" t="str">
         <f aca="false">IF($G10="","",MIN($G10,1.2)*$D10)</f>
         <v/>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="29" t="str">
+      <c r="A11" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B7</f>
-        <v>عملاء جدد لم يشتروا منّا</v>
-      </c>
-      <c r="C11" s="29" t="str">
+        <v>هامش المساهمة المتحقق</v>
+      </c>
+      <c r="C11" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F7</f>
         <v>أعلى أفضل</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G7</f>
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E11" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H7</f>
         <v>0</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="31" t="str">
+      <c r="F11" s="22"/>
+      <c r="G11" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F11="",$E11=""),"",IF($C11="أقل أفضل",$E11/$F11,$F11/$E11)),"")</f>
         <v/>
       </c>
-      <c r="H11" s="32" t="str">
+      <c r="H11" s="33" t="str">
         <f aca="false">IF($G11="","",MIN($G11,1.2)*$D11)</f>
         <v/>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="29" t="str">
+      <c r="A12" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B8</f>
-        <v>زيارات ميدانية مؤهَّلة</v>
-      </c>
-      <c r="C12" s="29" t="str">
+        <v>عملاء جدد لم يشتروا منّا</v>
+      </c>
+      <c r="C12" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F8</f>
         <v>أعلى أفضل</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G8</f>
-        <v>0.05</v>
-      </c>
-      <c r="E12" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E12" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H8</f>
         <v>0</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="31" t="str">
+      <c r="F12" s="22"/>
+      <c r="G12" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F12="",$E12=""),"",IF($C12="أقل أفضل",$E12/$F12,$F12/$E12)),"")</f>
         <v/>
       </c>
-      <c r="H12" s="32" t="str">
+      <c r="H12" s="33" t="str">
         <f aca="false">IF($G12="","",MIN($G12,1.2)*$D12)</f>
         <v/>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="29" t="str">
+      <c r="A13" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B9</f>
-        <v>عروض مقدَّمة</v>
-      </c>
-      <c r="C13" s="29" t="str">
+        <v>زيارات ميدانية مؤهَّلة</v>
+      </c>
+      <c r="C13" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F9</f>
         <v>أعلى أفضل</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G9</f>
         <v>0.05</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H9</f>
         <v>0</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="31" t="str">
+      <c r="F13" s="22"/>
+      <c r="G13" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F13="",$E13=""),"",IF($C13="أقل أفضل",$E13/$F13,$F13/$E13)),"")</f>
         <v/>
       </c>
-      <c r="H13" s="32" t="str">
+      <c r="H13" s="33" t="str">
         <f aca="false">IF($G13="","",MIN($G13,1.2)*$D13)</f>
         <v/>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="29" t="str">
+      <c r="A14" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B10</f>
-        <v>معدل التحويل</v>
-      </c>
-      <c r="C14" s="29" t="str">
+        <v>عروض مقدَّمة</v>
+      </c>
+      <c r="C14" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F10</f>
         <v>أعلى أفضل</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G10</f>
-        <v>0.08</v>
-      </c>
-      <c r="E14" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E14" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H10</f>
         <v>0</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="31" t="str">
+      <c r="F14" s="22"/>
+      <c r="G14" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F14="",$E14=""),"",IF($C14="أقل أفضل",$E14/$F14,$F14/$E14)),"")</f>
         <v/>
       </c>
-      <c r="H14" s="32" t="str">
+      <c r="H14" s="33" t="str">
         <f aca="false">IF($G14="","",MIN($G14,1.2)*$D14)</f>
         <v/>
       </c>
-      <c r="I14" s="21"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="29" t="str">
+      <c r="A15" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B11</f>
-        <v>متوسط الخصم الممنوح</v>
-      </c>
-      <c r="C15" s="29" t="str">
+        <v>معدل التحويل</v>
+      </c>
+      <c r="C15" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F11</f>
-        <v>أقل أفضل</v>
-      </c>
-      <c r="D15" s="30" t="n">
+        <v>أعلى أفضل</v>
+      </c>
+      <c r="D15" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G11</f>
-        <v>0.07</v>
-      </c>
-      <c r="E15" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E15" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H11</f>
         <v>0</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="31" t="str">
+      <c r="F15" s="22"/>
+      <c r="G15" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F15="",$E15=""),"",IF($C15="أقل أفضل",$E15/$F15,$F15/$E15)),"")</f>
         <v/>
       </c>
-      <c r="H15" s="32" t="str">
+      <c r="H15" s="33" t="str">
         <f aca="false">IF($G15="","",MIN($G15,1.2)*$D15)</f>
         <v/>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="29" t="str">
+      <c r="A16" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B12</f>
-        <v>أيام التحصيل</v>
-      </c>
-      <c r="C16" s="29" t="str">
+        <v>متوسط الخصم الممنوح</v>
+      </c>
+      <c r="C16" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F12</f>
         <v>أقل أفضل</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G12</f>
-        <v>0.05</v>
-      </c>
-      <c r="E16" s="29" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="E16" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H12</f>
         <v>0</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="31" t="str">
+      <c r="F16" s="22"/>
+      <c r="G16" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F16="",$E16=""),"",IF($C16="أقل أفضل",$E16/$F16,$F16/$E16)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="32" t="str">
+      <c r="H16" s="33" t="str">
         <f aca="false">IF($G16="","",MIN($G16,1.2)*$D16)</f>
         <v/>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="29" t="str">
+      <c r="A17" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B13</f>
-        <v>ديون متأخرة فوق ٩٠ يوماً</v>
-      </c>
-      <c r="C17" s="29" t="str">
+        <v>أيام التحصيل</v>
+      </c>
+      <c r="C17" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F13</f>
         <v>أقل أفضل</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G13</f>
-        <v>0.03</v>
-      </c>
-      <c r="E17" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H13</f>
         <v>0</v>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="31" t="str">
+      <c r="F17" s="22"/>
+      <c r="G17" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F17="",$E17=""),"",IF($C17="أقل أفضل",$E17/$F17,$F17/$E17)),"")</f>
         <v/>
       </c>
-      <c r="H17" s="32" t="str">
+      <c r="H17" s="33" t="str">
         <f aca="false">IF($G17="","",MIN($G17,1.2)*$D17)</f>
         <v/>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="29" t="str">
+      <c r="A18" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!B14</f>
-        <v>معدل تجديد العقود</v>
-      </c>
-      <c r="C18" s="29" t="str">
+        <v>ديون متأخرة فوق ٩٠ يوماً</v>
+      </c>
+      <c r="C18" s="30" t="str">
         <f aca="false">'مؤشرات الأداء'!F14</f>
-        <v>أعلى أفضل</v>
-      </c>
-      <c r="D18" s="30" t="n">
+        <v>أقل أفضل</v>
+      </c>
+      <c r="D18" s="31" t="n">
         <f aca="false">'مؤشرات الأداء'!G14</f>
-        <v>0.02</v>
-      </c>
-      <c r="E18" s="29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E18" s="30" t="n">
         <f aca="false">'مؤشرات الأداء'!H14</f>
         <v>0</v>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="31" t="str">
+      <c r="F18" s="22"/>
+      <c r="G18" s="32" t="str">
         <f aca="false">IFERROR(IF(OR($F18="",$E18=""),"",IF($C18="أقل أفضل",$E18/$F18,$F18/$E18)),"")</f>
         <v/>
       </c>
-      <c r="H18" s="32" t="str">
+      <c r="H18" s="33" t="str">
         <f aca="false">IF($G18="","",MIN($G18,1.2)*$D18)</f>
         <v/>
       </c>
-      <c r="I18" s="21"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25" t="n">
-        <f aca="false">SUM(D8:D18)</f>
+      <c r="I18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="30" t="str">
+        <f aca="false">'مؤشرات الأداء'!B15</f>
+        <v>معدل تجديد العقود</v>
+      </c>
+      <c r="C19" s="30" t="str">
+        <f aca="false">'مؤشرات الأداء'!F15</f>
+        <v>أعلى أفضل</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <f aca="false">'مؤشرات الأداء'!G15</f>
+        <v>0.02</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <f aca="false">'مؤشرات الأداء'!H15</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="32" t="str">
+        <f aca="false">IFERROR(IF(OR($F19="",$E19=""),"",IF($C19="أقل أفضل",$E19/$F19,$F19/$E19)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="33" t="str">
+        <f aca="false">IF($G19="","",MIN($G19,1.2)*$D19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="26" t="n">
+        <f aca="false">SUM(D9:D19)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="33" t="n">
-        <f aca="false">SUM(H8:H18)</f>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="34" t="n">
+        <f aca="false">SUM(H9:H19)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="24"/>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="I20" s="25"/>
+    </row>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="C23" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+      <c r="C24" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D24" s="12" t="s">
+      <c r="B25" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
+      <c r="C25" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="D25" s="12" t="s">
+      <c r="B26" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
+      <c r="C26" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>200</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="B27" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16" t="s">
+      <c r="C27" s="37" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="17" t="s">
+      <c r="D27" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="17" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C30" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
+      <c r="C30" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C31" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+      <c r="C31" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C32" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="C30:I30"/>
     <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C32:I32"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G18">
+  <conditionalFormatting sqref="G9:G19">
     <cfRule type="dataBar" priority="2">
       <dataBar showValue="1" minLength="10" maxLength="90">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1.2"/>
-        <color rgb="FF5B9BD5"/>
+        <color rgb="FFF5831F"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{CD80F6C6-7CBF-4AA8-8E39-449A23787D26}</x14:id>
+          <x14:id>{ACE74320-A1C3-465E-9FF3-B7D980AB33C0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
+  <conditionalFormatting sqref="H20">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>1</formula>
     </cfRule>
@@ -3340,9 +3412,9 @@
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3351,7 +3423,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{CD80F6C6-7CBF-4AA8-8E39-449A23787D26}">
+          <x14:cfRule type="dataBar" id="{ACE74320-A1C3-465E-9FF3-B7D980AB33C0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -3359,11 +3431,11 @@
               <x14:cfvo type="num">
                 <xm:f>1.2</xm:f>
               </x14:cfvo>
-              <x14:negativeFillColor rgb="FF5B9BD5"/>
+              <x14:negativeFillColor rgb="FFF5831F"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G8:G18</xm:sqref>
+          <xm:sqref>G9:G19</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
